--- a/improvement/manufacturing/plan-01.xlsx
+++ b/improvement/manufacturing/plan-01.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>28名（うち製造現場20名・検査3名）</t>
+          <t>18名（うち製造現場12名・検査2名）</t>
         </is>
       </c>
     </row>
